--- a/data/nzd0051/nzd0051.xlsx
+++ b/data/nzd0051/nzd0051.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J550"/>
+  <dimension ref="A1:J552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20238,6 +20238,78 @@
         <v>396.36</v>
       </c>
       <c r="J550" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>380.21</v>
+      </c>
+      <c r="C551" t="n">
+        <v>390.36</v>
+      </c>
+      <c r="D551" t="n">
+        <v>392.93</v>
+      </c>
+      <c r="E551" t="n">
+        <v>400.38</v>
+      </c>
+      <c r="F551" t="n">
+        <v>392.66</v>
+      </c>
+      <c r="G551" t="n">
+        <v>393.94</v>
+      </c>
+      <c r="H551" t="n">
+        <v>394.62</v>
+      </c>
+      <c r="I551" t="n">
+        <v>396.51</v>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>379.26</v>
+      </c>
+      <c r="C552" t="n">
+        <v>389.33</v>
+      </c>
+      <c r="D552" t="n">
+        <v>392.37</v>
+      </c>
+      <c r="E552" t="n">
+        <v>399.83</v>
+      </c>
+      <c r="F552" t="n">
+        <v>392.31</v>
+      </c>
+      <c r="G552" t="n">
+        <v>393.73</v>
+      </c>
+      <c r="H552" t="n">
+        <v>394.15</v>
+      </c>
+      <c r="I552" t="n">
+        <v>395.82</v>
+      </c>
+      <c r="J552" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20254,7 +20326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B575"/>
+  <dimension ref="A1:B577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26007,6 +26079,26 @@
       </c>
       <c r="B575" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>-0.48</v>
       </c>
     </row>
   </sheetData>
@@ -26175,28 +26267,28 @@
         <v>0.097</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1452266700052121</v>
+        <v>0.1417647685832576</v>
       </c>
       <c r="J2" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K2" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05216257005279867</v>
+        <v>0.05003366184050262</v>
       </c>
       <c r="M2" t="n">
-        <v>3.739707311979266</v>
+        <v>3.741388176430905</v>
       </c>
       <c r="N2" t="n">
-        <v>21.22900554066395</v>
+        <v>21.23375110999978</v>
       </c>
       <c r="O2" t="n">
-        <v>4.607494497084501</v>
+        <v>4.608009452030213</v>
       </c>
       <c r="P2" t="n">
-        <v>380.666465447415</v>
+        <v>380.701656727642</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26253,28 +26345,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2023560803862973</v>
+        <v>0.2012046504095696</v>
       </c>
       <c r="J3" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K3" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1770521823387757</v>
+        <v>0.1764472915135392</v>
       </c>
       <c r="M3" t="n">
-        <v>2.484980790157691</v>
+        <v>2.482006055774068</v>
       </c>
       <c r="N3" t="n">
-        <v>10.54303258415865</v>
+        <v>10.51469308688229</v>
       </c>
       <c r="O3" t="n">
-        <v>3.247003631682394</v>
+        <v>3.242636749141398</v>
       </c>
       <c r="P3" t="n">
-        <v>386.1013635426031</v>
+        <v>386.1130694592014</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26331,28 +26423,28 @@
         <v>0.1301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1704764861527288</v>
+        <v>0.168781630534961</v>
       </c>
       <c r="J4" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K4" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1596546639308989</v>
+        <v>0.157770260671532</v>
       </c>
       <c r="M4" t="n">
-        <v>1.8526453813206</v>
+        <v>1.853195007278828</v>
       </c>
       <c r="N4" t="n">
-        <v>8.473584650043833</v>
+        <v>8.462524792635353</v>
       </c>
       <c r="O4" t="n">
-        <v>2.910942227191023</v>
+        <v>2.909041902866879</v>
       </c>
       <c r="P4" t="n">
-        <v>390.4883142596036</v>
+        <v>390.5055431564102</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26409,28 +26501,28 @@
         <v>0.1363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2229867172405231</v>
+        <v>0.2206657116719758</v>
       </c>
       <c r="J5" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K5" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2758215010985554</v>
+        <v>0.2722793793207462</v>
       </c>
       <c r="M5" t="n">
-        <v>2.163129977255128</v>
+        <v>2.166264923421596</v>
       </c>
       <c r="N5" t="n">
-        <v>7.231651926314506</v>
+        <v>7.242088174898078</v>
       </c>
       <c r="O5" t="n">
-        <v>2.689173093408921</v>
+        <v>2.691112813484057</v>
       </c>
       <c r="P5" t="n">
-        <v>397.4211925463422</v>
+        <v>397.4447861347874</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26487,28 +26579,28 @@
         <v>0.1141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1173419055550518</v>
+        <v>0.1140410654870996</v>
       </c>
       <c r="J6" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K6" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08837753628436407</v>
+        <v>0.08379731185161188</v>
       </c>
       <c r="M6" t="n">
-        <v>2.290048826744241</v>
+        <v>2.296641937625608</v>
       </c>
       <c r="N6" t="n">
-        <v>7.867584551647178</v>
+        <v>7.912763319929152</v>
       </c>
       <c r="O6" t="n">
-        <v>2.804921487608375</v>
+        <v>2.812963440915853</v>
       </c>
       <c r="P6" t="n">
-        <v>393.9278799097532</v>
+        <v>393.9614329511998</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26565,28 +26657,28 @@
         <v>0.1124</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03248367596136657</v>
+        <v>0.02948810611245307</v>
       </c>
       <c r="J7" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K7" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006111817809032249</v>
+        <v>0.00505108529517162</v>
       </c>
       <c r="M7" t="n">
-        <v>2.489536254056187</v>
+        <v>2.495591183027608</v>
       </c>
       <c r="N7" t="n">
-        <v>9.505161146331515</v>
+        <v>9.531341059974665</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08304413629314</v>
+        <v>3.087287006414315</v>
       </c>
       <c r="P7" t="n">
-        <v>397.0944139189674</v>
+        <v>397.1248637082676</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26643,28 +26735,28 @@
         <v>0.0858</v>
       </c>
       <c r="I8" t="n">
-        <v>0.006010535742143963</v>
+        <v>0.003479586393657739</v>
       </c>
       <c r="J8" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K8" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002083359566464882</v>
+        <v>7.008780786665891e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.423505677357751</v>
+        <v>2.426825211464561</v>
       </c>
       <c r="N8" t="n">
-        <v>9.620125845279645</v>
+        <v>9.628730043890725</v>
       </c>
       <c r="O8" t="n">
-        <v>3.101632770861122</v>
+        <v>3.103019504271722</v>
       </c>
       <c r="P8" t="n">
-        <v>397.7000471929319</v>
+        <v>397.7257576985401</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26721,28 +26813,28 @@
         <v>0.0939</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02154349125303836</v>
+        <v>0.01998885467557242</v>
       </c>
       <c r="J9" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K9" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002406657028647285</v>
+        <v>0.002086275386842584</v>
       </c>
       <c r="M9" t="n">
-        <v>2.577684412412908</v>
+        <v>2.573460348286215</v>
       </c>
       <c r="N9" t="n">
-        <v>10.67531289499125</v>
+        <v>10.65329275824648</v>
       </c>
       <c r="O9" t="n">
-        <v>3.267309733556226</v>
+        <v>3.263938228313532</v>
       </c>
       <c r="P9" t="n">
-        <v>397.7307616503627</v>
+        <v>397.7465550488012</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26780,7 +26872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J550"/>
+  <dimension ref="A1:J552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55375,6 +55467,110 @@
         </is>
       </c>
     </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-35.02108713987465,173.86594047995078</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>-35.02094857002104,173.86682402574695</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>-35.02085360470865,173.86770734016554</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-35.02071051090179,173.8685416560093</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-35.02054409074449,173.86936468528728</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>-35.020265482506304,173.87014524098885</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>-35.01988746431485,173.87082408525103</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>-35.019360881481724,173.87134859396787</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-35.021095684437675,173.86594121410798</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-35.02095782159966,173.86682501381344</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-35.020858622187056,173.8677080288227</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-35.0207153351432,173.8685430527637</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>-35.02054702648773,173.86936609284828</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>-35.02026714219117,173.87014634898668</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>-35.019890618309624,173.87082752593997</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>-35.01936491024004,173.8713543569119</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0051/nzd0051.xlsx
+++ b/data/nzd0051/nzd0051.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J552"/>
+  <dimension ref="A1:J555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20312,6 +20312,114 @@
       <c r="J552" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>378.44</v>
+      </c>
+      <c r="C553" t="n">
+        <v>388.74</v>
+      </c>
+      <c r="D553" t="n">
+        <v>391.53</v>
+      </c>
+      <c r="E553" t="n">
+        <v>398.67</v>
+      </c>
+      <c r="F553" t="n">
+        <v>392.06</v>
+      </c>
+      <c r="G553" t="n">
+        <v>394.42</v>
+      </c>
+      <c r="H553" t="n">
+        <v>394.63</v>
+      </c>
+      <c r="I553" t="n">
+        <v>394.91</v>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>378.84</v>
+      </c>
+      <c r="C554" t="n">
+        <v>389.26</v>
+      </c>
+      <c r="D554" t="n">
+        <v>392.05</v>
+      </c>
+      <c r="E554" t="n">
+        <v>399.58</v>
+      </c>
+      <c r="F554" t="n">
+        <v>392.68</v>
+      </c>
+      <c r="G554" t="n">
+        <v>395.09</v>
+      </c>
+      <c r="H554" t="n">
+        <v>395.32</v>
+      </c>
+      <c r="I554" t="n">
+        <v>395.08</v>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>378.28</v>
+      </c>
+      <c r="C555" t="n">
+        <v>388.8</v>
+      </c>
+      <c r="D555" t="n">
+        <v>391.58</v>
+      </c>
+      <c r="E555" t="n">
+        <v>399.52</v>
+      </c>
+      <c r="F555" t="n">
+        <v>392.5</v>
+      </c>
+      <c r="G555" t="n">
+        <v>395.26</v>
+      </c>
+      <c r="H555" t="n">
+        <v>394.99</v>
+      </c>
+      <c r="I555" t="n">
+        <v>393.96</v>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20326,7 +20434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B577"/>
+  <dimension ref="A1:B580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26099,6 +26207,36 @@
       </c>
       <c r="B577" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>-0.03</v>
       </c>
     </row>
   </sheetData>
@@ -26267,28 +26405,28 @@
         <v>0.097</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1417647685832576</v>
+        <v>0.135353594684074</v>
       </c>
       <c r="J2" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K2" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05003366184050262</v>
+        <v>0.04596339062171173</v>
       </c>
       <c r="M2" t="n">
-        <v>3.741388176430905</v>
+        <v>3.749003422185024</v>
       </c>
       <c r="N2" t="n">
-        <v>21.23375110999978</v>
+        <v>21.30587578194653</v>
       </c>
       <c r="O2" t="n">
-        <v>4.608009452030213</v>
+        <v>4.615828829359526</v>
       </c>
       <c r="P2" t="n">
-        <v>380.701656727642</v>
+        <v>380.7670693862406</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26345,28 +26483,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2012046504095696</v>
+        <v>0.1985060858704606</v>
       </c>
       <c r="J3" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K3" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1764472915135392</v>
+        <v>0.1738551479325641</v>
       </c>
       <c r="M3" t="n">
-        <v>2.482006055774068</v>
+        <v>2.482582569670297</v>
       </c>
       <c r="N3" t="n">
-        <v>10.51469308688229</v>
+        <v>10.49115053219223</v>
       </c>
       <c r="O3" t="n">
-        <v>3.242636749141398</v>
+        <v>3.239004558840914</v>
       </c>
       <c r="P3" t="n">
-        <v>386.1130694592014</v>
+        <v>386.140602742441</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26423,28 +26561,28 @@
         <v>0.1301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.168781630534961</v>
+        <v>0.1652757405656992</v>
       </c>
       <c r="J4" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K4" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L4" t="n">
-        <v>0.157770260671532</v>
+        <v>0.1529961339629474</v>
       </c>
       <c r="M4" t="n">
-        <v>1.853195007278828</v>
+        <v>1.858226121862923</v>
       </c>
       <c r="N4" t="n">
-        <v>8.462524792635353</v>
+        <v>8.472859009997581</v>
       </c>
       <c r="O4" t="n">
-        <v>2.909041902866879</v>
+        <v>2.910817584459318</v>
       </c>
       <c r="P4" t="n">
-        <v>390.5055431564102</v>
+        <v>390.541313440263</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26501,28 +26639,28 @@
         <v>0.1363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2206657116719758</v>
+        <v>0.2163230222841031</v>
       </c>
       <c r="J5" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K5" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2722793793207462</v>
+        <v>0.2645313717095024</v>
       </c>
       <c r="M5" t="n">
-        <v>2.166264923421596</v>
+        <v>2.175029597647135</v>
       </c>
       <c r="N5" t="n">
-        <v>7.242088174898078</v>
+        <v>7.289525719637092</v>
       </c>
       <c r="O5" t="n">
-        <v>2.691112813484057</v>
+        <v>2.69991216887459</v>
       </c>
       <c r="P5" t="n">
-        <v>397.4447861347874</v>
+        <v>397.4890925175665</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26579,28 +26717,28 @@
         <v>0.1141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1140410654870996</v>
+        <v>0.1091119407558985</v>
       </c>
       <c r="J6" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K6" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08379731185161188</v>
+        <v>0.07713439901237906</v>
       </c>
       <c r="M6" t="n">
-        <v>2.296641937625608</v>
+        <v>2.30644416345571</v>
       </c>
       <c r="N6" t="n">
-        <v>7.912763319929152</v>
+        <v>7.98071385556926</v>
       </c>
       <c r="O6" t="n">
-        <v>2.812963440915853</v>
+        <v>2.825015726605652</v>
       </c>
       <c r="P6" t="n">
-        <v>393.9614329511998</v>
+        <v>394.0117233236612</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26657,28 +26795,28 @@
         <v>0.1124</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02948810611245307</v>
+        <v>0.02626329785777443</v>
       </c>
       <c r="J7" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K7" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00505108529517162</v>
+        <v>0.004039788273934475</v>
       </c>
       <c r="M7" t="n">
-        <v>2.495591183027608</v>
+        <v>2.498348973216383</v>
       </c>
       <c r="N7" t="n">
-        <v>9.531341059974665</v>
+        <v>9.527714241573944</v>
       </c>
       <c r="O7" t="n">
-        <v>3.087287006414315</v>
+        <v>3.086699570993903</v>
       </c>
       <c r="P7" t="n">
-        <v>397.1248637082676</v>
+        <v>397.1577643314653</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26735,28 +26873,28 @@
         <v>0.0858</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003479586393657739</v>
+        <v>0.0004113668858470144</v>
       </c>
       <c r="J8" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K8" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L8" t="n">
-        <v>7.008780786665891e-05</v>
+        <v>9.872672579458452e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>2.426825211464561</v>
+        <v>2.428240701734512</v>
       </c>
       <c r="N8" t="n">
-        <v>9.628730043890725</v>
+        <v>9.619798476456388</v>
       </c>
       <c r="O8" t="n">
-        <v>3.103019504271722</v>
+        <v>3.101579996784927</v>
       </c>
       <c r="P8" t="n">
-        <v>397.7257576985401</v>
+        <v>397.7570415874891</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26813,28 +26951,28 @@
         <v>0.0939</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01998885467557242</v>
+        <v>0.0160686726413502</v>
       </c>
       <c r="J9" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="K9" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002086275386842584</v>
+        <v>0.001356683289227001</v>
       </c>
       <c r="M9" t="n">
-        <v>2.573460348286215</v>
+        <v>2.572387518163717</v>
       </c>
       <c r="N9" t="n">
-        <v>10.65329275824648</v>
+        <v>10.66680631896847</v>
       </c>
       <c r="O9" t="n">
-        <v>3.263938228313532</v>
+        <v>3.266007703445978</v>
       </c>
       <c r="P9" t="n">
-        <v>397.7465550488012</v>
+        <v>397.7865284510227</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26872,7 +27010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J552"/>
+  <dimension ref="A1:J555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55571,6 +55709,162 @@
         </is>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-35.021103059744696,173.8659418478017</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-35.020963121047615,173.86682557979339</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-35.02086614840466,173.86770906180868</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-35.02072550990682,173.86854599864625</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>-35.02054912344716,173.86936709824906</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>-35.02026168894087,173.8701427084226</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>-35.019887397208564,173.8708240120449</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>-35.01937022352958,173.87136195731728</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-35.021099462033945,173.8659415386828</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-35.020958450347734,173.8668250809636</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-35.02086148931759,173.86770842234117</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-35.020717527980196,173.8685436876521</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-35.02054392298774,173.86936460485524</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>-35.02025639375568,173.8701391733826</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>-35.01988276687562,173.8708189608212</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>-35.019369230937066,173.87136053746124</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-35.02110449882898,173.86594197144927</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-35.0209625821207,173.8668255222361</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-35.02086570041552,173.86770900032144</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>-35.020718054261074,173.86854384002535</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>-35.02054543279855,173.86936532874373</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>-35.020255050201214,173.87013827643221</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>-35.01988498138271,173.87082137662375</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>-35.01937577036978,173.87136989180743</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0051/nzd0051.xlsx
+++ b/data/nzd0051/nzd0051.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J555"/>
+  <dimension ref="A1:J556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20418,6 +20418,42 @@
         <v>393.96</v>
       </c>
       <c r="J555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>377.1</v>
+      </c>
+      <c r="C556" t="n">
+        <v>386.68</v>
+      </c>
+      <c r="D556" t="n">
+        <v>389.67</v>
+      </c>
+      <c r="E556" t="n">
+        <v>396.82</v>
+      </c>
+      <c r="F556" t="n">
+        <v>389.93</v>
+      </c>
+      <c r="G556" t="n">
+        <v>394.08</v>
+      </c>
+      <c r="H556" t="n">
+        <v>394.68</v>
+      </c>
+      <c r="I556" t="n">
+        <v>394.44</v>
+      </c>
+      <c r="J556" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20434,7 +20470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B580"/>
+  <dimension ref="A1:B581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26237,6 +26273,16 @@
       </c>
       <c r="B580" t="n">
         <v>-0.03</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
@@ -26405,28 +26451,28 @@
         <v>0.097</v>
       </c>
       <c r="I2" t="n">
-        <v>0.135353594684074</v>
+        <v>0.1327468821605625</v>
       </c>
       <c r="J2" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K2" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04596339062171173</v>
+        <v>0.04427211885232973</v>
       </c>
       <c r="M2" t="n">
-        <v>3.749003422185024</v>
+        <v>3.753643819083392</v>
       </c>
       <c r="N2" t="n">
-        <v>21.30587578194653</v>
+        <v>21.36159062213571</v>
       </c>
       <c r="O2" t="n">
-        <v>4.615828829359526</v>
+        <v>4.621860082492297</v>
       </c>
       <c r="P2" t="n">
-        <v>380.7670693862406</v>
+        <v>380.7937054192427</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26483,28 +26529,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1985060858704606</v>
+        <v>0.1968140704179156</v>
       </c>
       <c r="J3" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K3" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1738551479325641</v>
+        <v>0.1714478513690332</v>
       </c>
       <c r="M3" t="n">
-        <v>2.482582569670297</v>
+        <v>2.48696282856501</v>
       </c>
       <c r="N3" t="n">
-        <v>10.49115053219223</v>
+        <v>10.51189631371906</v>
       </c>
       <c r="O3" t="n">
-        <v>3.239004558840914</v>
+        <v>3.242205470620124</v>
       </c>
       <c r="P3" t="n">
-        <v>386.140602742441</v>
+        <v>386.1578921746387</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26561,28 +26607,28 @@
         <v>0.1301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1652757405656992</v>
+        <v>0.163389291841991</v>
       </c>
       <c r="J4" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K4" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1529961339629474</v>
+        <v>0.1498197335493502</v>
       </c>
       <c r="M4" t="n">
-        <v>1.858226121862923</v>
+        <v>1.863003595825727</v>
       </c>
       <c r="N4" t="n">
-        <v>8.472859009997581</v>
+        <v>8.506877161462658</v>
       </c>
       <c r="O4" t="n">
-        <v>2.910817584459318</v>
+        <v>2.916655132418411</v>
       </c>
       <c r="P4" t="n">
-        <v>390.541313440263</v>
+        <v>390.5605896396936</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26639,28 +26685,28 @@
         <v>0.1363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2163230222841031</v>
+        <v>0.2140253926014221</v>
       </c>
       <c r="J5" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K5" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2645313717095024</v>
+        <v>0.2592529005972768</v>
       </c>
       <c r="M5" t="n">
-        <v>2.175029597647135</v>
+        <v>2.182042663051056</v>
       </c>
       <c r="N5" t="n">
-        <v>7.289525719637092</v>
+        <v>7.349502144792812</v>
       </c>
       <c r="O5" t="n">
-        <v>2.69991216887459</v>
+        <v>2.710996522460479</v>
       </c>
       <c r="P5" t="n">
-        <v>397.4890925175665</v>
+        <v>397.5125702656888</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26717,28 +26763,28 @@
         <v>0.1141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1091119407558985</v>
+        <v>0.1066081010890206</v>
       </c>
       <c r="J6" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K6" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07713439901237906</v>
+        <v>0.07342998991892813</v>
       </c>
       <c r="M6" t="n">
-        <v>2.30644416345571</v>
+        <v>2.313709931013887</v>
       </c>
       <c r="N6" t="n">
-        <v>7.98071385556926</v>
+        <v>8.053157021569353</v>
       </c>
       <c r="O6" t="n">
-        <v>2.825015726605652</v>
+        <v>2.83780848923414</v>
       </c>
       <c r="P6" t="n">
-        <v>394.0117233236612</v>
+        <v>394.0373081763818</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26795,28 +26841,28 @@
         <v>0.1124</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02626329785777443</v>
+        <v>0.02490573345657499</v>
       </c>
       <c r="J7" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K7" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004039788273934475</v>
+        <v>0.003639374462591438</v>
       </c>
       <c r="M7" t="n">
-        <v>2.498348973216383</v>
+        <v>2.500723519607746</v>
       </c>
       <c r="N7" t="n">
-        <v>9.527714241573944</v>
+        <v>9.536070780790583</v>
       </c>
       <c r="O7" t="n">
-        <v>3.086699570993903</v>
+        <v>3.088052910944141</v>
       </c>
       <c r="P7" t="n">
-        <v>397.1577643314653</v>
+        <v>397.1716362601366</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26873,28 +26919,28 @@
         <v>0.0858</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004113668858470144</v>
+        <v>-0.0006972951655618185</v>
       </c>
       <c r="J8" t="n">
+        <v>555</v>
+      </c>
+      <c r="K8" t="n">
         <v>554</v>
       </c>
-      <c r="K8" t="n">
-        <v>553</v>
-      </c>
       <c r="L8" t="n">
-        <v>9.872672579458452e-07</v>
+        <v>2.843113636075145e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>2.428240701734512</v>
+        <v>2.429098715375912</v>
       </c>
       <c r="N8" t="n">
-        <v>9.619798476456388</v>
+        <v>9.61949373093096</v>
       </c>
       <c r="O8" t="n">
-        <v>3.101579996784927</v>
+        <v>3.101530868930851</v>
       </c>
       <c r="P8" t="n">
-        <v>397.7570415874891</v>
+        <v>397.7683628706559</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26951,28 +26997,28 @@
         <v>0.0939</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0160686726413502</v>
+        <v>0.01471130919315107</v>
       </c>
       <c r="J9" t="n">
+        <v>555</v>
+      </c>
+      <c r="K9" t="n">
         <v>554</v>
       </c>
-      <c r="K9" t="n">
-        <v>553</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.001356683289227001</v>
+        <v>0.001139279783209601</v>
       </c>
       <c r="M9" t="n">
-        <v>2.572387518163717</v>
+        <v>2.572254232243757</v>
       </c>
       <c r="N9" t="n">
-        <v>10.66680631896847</v>
+        <v>10.6731239106851</v>
       </c>
       <c r="O9" t="n">
-        <v>3.266007703445978</v>
+        <v>3.266974733707792</v>
       </c>
       <c r="P9" t="n">
-        <v>397.7865284510227</v>
+        <v>397.8003893890224</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27010,7 +27056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J555"/>
+  <dimension ref="A1:J556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55865,6 +55911,58 @@
         </is>
       </c>
     </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-35.02111511207564,173.86594288335027</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-35.02098162420477,173.86682755592736</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-35.02088281360068,173.8677113491355</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-35.02074173690033,173.8685506968226</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>-35.020566989541216,173.8693756642659</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>-35.020264376049724,173.87014450232368</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>-35.019887061677196,173.87082364601417</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>-35.01937296775584,173.87136588280174</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0051/nzd0051.xlsx
+++ b/data/nzd0051/nzd0051.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J556"/>
+  <dimension ref="A1:J557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20454,6 +20454,42 @@
         <v>394.44</v>
       </c>
       <c r="J556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>379.61</v>
+      </c>
+      <c r="C557" t="n">
+        <v>386.34</v>
+      </c>
+      <c r="D557" t="n">
+        <v>390.66</v>
+      </c>
+      <c r="E557" t="n">
+        <v>397.92</v>
+      </c>
+      <c r="F557" t="n">
+        <v>392.94</v>
+      </c>
+      <c r="G557" t="n">
+        <v>396.56</v>
+      </c>
+      <c r="H557" t="n">
+        <v>397.98</v>
+      </c>
+      <c r="I557" t="n">
+        <v>395.46</v>
+      </c>
+      <c r="J557" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20470,7 +20506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B581"/>
+  <dimension ref="A1:B582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26283,6 +26319,16 @@
       </c>
       <c r="B581" t="n">
         <v>0.86</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
@@ -26451,28 +26497,28 @@
         <v>0.097</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1327468821605625</v>
+        <v>0.1310516265980701</v>
       </c>
       <c r="J2" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K2" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04427211885232973</v>
+        <v>0.04328913762216624</v>
       </c>
       <c r="M2" t="n">
-        <v>3.753643819083392</v>
+        <v>3.754324923369196</v>
       </c>
       <c r="N2" t="n">
-        <v>21.36159062213571</v>
+        <v>21.36274725640416</v>
       </c>
       <c r="O2" t="n">
-        <v>4.621860082492297</v>
+        <v>4.621985207289629</v>
       </c>
       <c r="P2" t="n">
-        <v>380.7937054192427</v>
+        <v>380.8110938317084</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26529,28 +26575,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1968140704179156</v>
+        <v>0.1949969729125493</v>
       </c>
       <c r="J3" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K3" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1714478513690332</v>
+        <v>0.1687942407205264</v>
       </c>
       <c r="M3" t="n">
-        <v>2.48696282856501</v>
+        <v>2.491967625512319</v>
       </c>
       <c r="N3" t="n">
-        <v>10.51189631371906</v>
+        <v>10.53846017252565</v>
       </c>
       <c r="O3" t="n">
-        <v>3.242205470620124</v>
+        <v>3.246299458233274</v>
       </c>
       <c r="P3" t="n">
-        <v>386.1578921746387</v>
+        <v>386.1765303325736</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26607,28 +26653,28 @@
         <v>0.1301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.163389291841991</v>
+        <v>0.1618617151513916</v>
       </c>
       <c r="J4" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K4" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1498197335493502</v>
+        <v>0.1474804238382653</v>
       </c>
       <c r="M4" t="n">
-        <v>1.863003595825727</v>
+        <v>1.866168725355142</v>
       </c>
       <c r="N4" t="n">
-        <v>8.506877161462658</v>
+        <v>8.523711847811876</v>
       </c>
       <c r="O4" t="n">
-        <v>2.916655132418411</v>
+        <v>2.919539663681909</v>
       </c>
       <c r="P4" t="n">
-        <v>390.5605896396936</v>
+        <v>390.5762581525461</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26685,28 +26731,28 @@
         <v>0.1363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2140253926014221</v>
+        <v>0.212124849403396</v>
       </c>
       <c r="J5" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K5" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2592529005972768</v>
+        <v>0.255332094056019</v>
       </c>
       <c r="M5" t="n">
-        <v>2.182042663051056</v>
+        <v>2.187168030099575</v>
       </c>
       <c r="N5" t="n">
-        <v>7.349502144792812</v>
+        <v>7.386025861162099</v>
       </c>
       <c r="O5" t="n">
-        <v>2.710996522460479</v>
+        <v>2.71772439021364</v>
       </c>
       <c r="P5" t="n">
-        <v>397.5125702656888</v>
+        <v>397.5320643347645</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26763,28 +26809,28 @@
         <v>0.1141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1066081010890206</v>
+        <v>0.1051928980618847</v>
       </c>
       <c r="J6" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K6" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07342998991892813</v>
+        <v>0.07167558286727738</v>
       </c>
       <c r="M6" t="n">
-        <v>2.313709931013887</v>
+        <v>2.31605932995415</v>
       </c>
       <c r="N6" t="n">
-        <v>8.053157021569353</v>
+        <v>8.066253760117318</v>
       </c>
       <c r="O6" t="n">
-        <v>2.83780848923414</v>
+        <v>2.840115096279959</v>
       </c>
       <c r="P6" t="n">
-        <v>394.0373081763818</v>
+        <v>394.0518240608909</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26841,28 +26887,28 @@
         <v>0.1124</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02490573345657499</v>
+        <v>0.02444580392311303</v>
       </c>
       <c r="J7" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K7" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003639374462591438</v>
+        <v>0.003519875031251618</v>
       </c>
       <c r="M7" t="n">
-        <v>2.500723519607746</v>
+        <v>2.498545067200136</v>
       </c>
       <c r="N7" t="n">
-        <v>9.536070780790583</v>
+        <v>9.521832654882804</v>
       </c>
       <c r="O7" t="n">
-        <v>3.088052910944141</v>
+        <v>3.085746693246677</v>
       </c>
       <c r="P7" t="n">
-        <v>397.1716362601366</v>
+        <v>397.1763538051545</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26919,28 +26965,28 @@
         <v>0.0858</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0006972951655618185</v>
+        <v>-0.0006135556824233397</v>
       </c>
       <c r="J8" t="n">
+        <v>556</v>
+      </c>
+      <c r="K8" t="n">
         <v>555</v>
       </c>
-      <c r="K8" t="n">
-        <v>554</v>
-      </c>
       <c r="L8" t="n">
-        <v>2.843113636075145e-06</v>
+        <v>2.21021860646875e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>2.429098715375912</v>
+        <v>2.425162909462908</v>
       </c>
       <c r="N8" t="n">
-        <v>9.61949373093096</v>
+        <v>9.602258087516853</v>
       </c>
       <c r="O8" t="n">
-        <v>3.101530868930851</v>
+        <v>3.098751052846429</v>
       </c>
       <c r="P8" t="n">
-        <v>397.7683628706559</v>
+        <v>397.7675044899652</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26997,28 +27043,28 @@
         <v>0.0939</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01471130919315107</v>
+        <v>0.01372730010289698</v>
       </c>
       <c r="J9" t="n">
+        <v>556</v>
+      </c>
+      <c r="K9" t="n">
         <v>555</v>
       </c>
-      <c r="K9" t="n">
-        <v>554</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.001139279783209601</v>
+        <v>0.0009949169339719122</v>
       </c>
       <c r="M9" t="n">
-        <v>2.572254232243757</v>
+        <v>2.57091589620798</v>
       </c>
       <c r="N9" t="n">
-        <v>10.6731239106851</v>
+        <v>10.66725633676475</v>
       </c>
       <c r="O9" t="n">
-        <v>3.266974733707792</v>
+        <v>3.266076596891865</v>
       </c>
       <c r="P9" t="n">
-        <v>397.8003893890224</v>
+        <v>397.8104760813545</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27056,7 +27102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J556"/>
+  <dimension ref="A1:J557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55963,6 +56009,58 @@
         </is>
       </c>
     </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-35.02109253644077,173.865940943629</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-35.02098467812393,173.86682788208552</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-35.020873943415715,173.86771013168723</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-35.02073208841772,173.8685479033121</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>-35.02054174214988,173.86936355923854</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-35.020244775960926,173.87013141740093</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-35.01986491660448,173.8707994879931</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>-35.0193670122008,173.87135736366557</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0051/nzd0051.xlsx
+++ b/data/nzd0051/nzd0051.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J557"/>
+  <dimension ref="A1:J561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20492,6 +20492,150 @@
       <c r="J557" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>380.29</v>
+      </c>
+      <c r="C558" t="n">
+        <v>386.91</v>
+      </c>
+      <c r="D558" t="n">
+        <v>392</v>
+      </c>
+      <c r="E558" t="n">
+        <v>398.58</v>
+      </c>
+      <c r="F558" t="n">
+        <v>393.91</v>
+      </c>
+      <c r="G558" t="n">
+        <v>397.1</v>
+      </c>
+      <c r="H558" t="n">
+        <v>398.45</v>
+      </c>
+      <c r="I558" t="n">
+        <v>396.44</v>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>378.81</v>
+      </c>
+      <c r="C559" t="n">
+        <v>385.86</v>
+      </c>
+      <c r="D559" t="n">
+        <v>391.74</v>
+      </c>
+      <c r="E559" t="n">
+        <v>398.27</v>
+      </c>
+      <c r="F559" t="n">
+        <v>393.94</v>
+      </c>
+      <c r="G559" t="n">
+        <v>396.76</v>
+      </c>
+      <c r="H559" t="n">
+        <v>398.54</v>
+      </c>
+      <c r="I559" t="n">
+        <v>397.01</v>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>379.19</v>
+      </c>
+      <c r="C560" t="n">
+        <v>386.36</v>
+      </c>
+      <c r="D560" t="n">
+        <v>391.91</v>
+      </c>
+      <c r="E560" t="n">
+        <v>398.74</v>
+      </c>
+      <c r="F560" t="n">
+        <v>394.28</v>
+      </c>
+      <c r="G560" t="n">
+        <v>397.14</v>
+      </c>
+      <c r="H560" t="n">
+        <v>398.71</v>
+      </c>
+      <c r="I560" t="n">
+        <v>397.32</v>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>379.36</v>
+      </c>
+      <c r="C561" t="n">
+        <v>386.8</v>
+      </c>
+      <c r="D561" t="n">
+        <v>392.13</v>
+      </c>
+      <c r="E561" t="n">
+        <v>398.7</v>
+      </c>
+      <c r="F561" t="n">
+        <v>394.54</v>
+      </c>
+      <c r="G561" t="n">
+        <v>397.14</v>
+      </c>
+      <c r="H561" t="n">
+        <v>398.57</v>
+      </c>
+      <c r="I561" t="n">
+        <v>397.42</v>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20506,7 +20650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B582"/>
+  <dimension ref="A1:B586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26329,6 +26473,46 @@
       </c>
       <c r="B582" t="n">
         <v>0.06</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -26497,28 +26681,28 @@
         <v>0.097</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1310516265980701</v>
+        <v>0.1240900159193603</v>
       </c>
       <c r="J2" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="K2" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04328913762216624</v>
+        <v>0.03930390971321052</v>
       </c>
       <c r="M2" t="n">
-        <v>3.754324923369196</v>
+        <v>3.757736968087563</v>
       </c>
       <c r="N2" t="n">
-        <v>21.36274725640416</v>
+        <v>21.37906920281385</v>
       </c>
       <c r="O2" t="n">
-        <v>4.621985207289629</v>
+        <v>4.623750555859804</v>
       </c>
       <c r="P2" t="n">
-        <v>380.8110938317084</v>
+        <v>380.8828921013596</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26575,28 +26759,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1949969729125493</v>
+        <v>0.1880378235898751</v>
       </c>
       <c r="J3" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="K3" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1687942407205264</v>
+        <v>0.1589001457599236</v>
       </c>
       <c r="M3" t="n">
-        <v>2.491967625512319</v>
+        <v>2.509951421271341</v>
       </c>
       <c r="N3" t="n">
-        <v>10.53846017252565</v>
+        <v>10.63110815930973</v>
       </c>
       <c r="O3" t="n">
-        <v>3.246299458233274</v>
+        <v>3.260538016847792</v>
       </c>
       <c r="P3" t="n">
-        <v>386.1765303325736</v>
+        <v>386.2482987460758</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26653,28 +26837,28 @@
         <v>0.1301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1618617151513916</v>
+        <v>0.1576692540088065</v>
       </c>
       <c r="J4" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="K4" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1474804238382653</v>
+        <v>0.1421238067550366</v>
       </c>
       <c r="M4" t="n">
-        <v>1.866168725355142</v>
+        <v>1.870637609459106</v>
       </c>
       <c r="N4" t="n">
-        <v>8.523711847811876</v>
+        <v>8.523474238829706</v>
       </c>
       <c r="O4" t="n">
-        <v>2.919539663681909</v>
+        <v>2.919498970513555</v>
       </c>
       <c r="P4" t="n">
-        <v>390.5762581525461</v>
+        <v>390.6194928746608</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26731,28 +26915,28 @@
         <v>0.1363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.212124849403396</v>
+        <v>0.2055590174277734</v>
       </c>
       <c r="J5" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="K5" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="L5" t="n">
-        <v>0.255332094056019</v>
+        <v>0.2428789992557634</v>
       </c>
       <c r="M5" t="n">
-        <v>2.187168030099575</v>
+        <v>2.202703298399464</v>
       </c>
       <c r="N5" t="n">
-        <v>7.386025861162099</v>
+        <v>7.481923041870653</v>
       </c>
       <c r="O5" t="n">
-        <v>2.71772439021364</v>
+        <v>2.735310410514802</v>
       </c>
       <c r="P5" t="n">
-        <v>397.5320643347645</v>
+        <v>397.5997743430851</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26809,28 +26993,28 @@
         <v>0.1141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1051928980618847</v>
+        <v>0.1013666920292724</v>
       </c>
       <c r="J6" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="K6" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07167558286727738</v>
+        <v>0.06752774446617893</v>
       </c>
       <c r="M6" t="n">
-        <v>2.31605932995415</v>
+        <v>2.316810928932479</v>
       </c>
       <c r="N6" t="n">
-        <v>8.066253760117318</v>
+        <v>8.059517931677675</v>
       </c>
       <c r="O6" t="n">
-        <v>2.840115096279959</v>
+        <v>2.838929011383989</v>
       </c>
       <c r="P6" t="n">
-        <v>394.0518240608909</v>
+        <v>394.0912788677278</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26887,28 +27071,28 @@
         <v>0.1124</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02444580392311303</v>
+        <v>0.02331824556320504</v>
       </c>
       <c r="J7" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="K7" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003519875031251618</v>
+        <v>0.003254798743145715</v>
       </c>
       <c r="M7" t="n">
-        <v>2.498545067200136</v>
+        <v>2.486284620800356</v>
       </c>
       <c r="N7" t="n">
-        <v>9.521832654882804</v>
+        <v>9.458376545238412</v>
       </c>
       <c r="O7" t="n">
-        <v>3.085746693246677</v>
+        <v>3.075447373186284</v>
       </c>
       <c r="P7" t="n">
-        <v>397.1763538051545</v>
+        <v>397.1879818137725</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26965,28 +27149,28 @@
         <v>0.0858</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0006135556824233397</v>
+        <v>0.0005493376829237027</v>
       </c>
       <c r="J8" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="K8" t="n">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="L8" t="n">
-        <v>2.21021860646875e-06</v>
+        <v>1.800093146875348e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>2.425162909462908</v>
+        <v>2.413826895468112</v>
       </c>
       <c r="N8" t="n">
-        <v>9.602258087516853</v>
+        <v>9.538275306910426</v>
       </c>
       <c r="O8" t="n">
-        <v>3.098751052846429</v>
+        <v>3.088409834673894</v>
       </c>
       <c r="P8" t="n">
-        <v>397.7675044899652</v>
+        <v>397.7555186429801</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27043,28 +27227,28 @@
         <v>0.0939</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01372730010289698</v>
+        <v>0.01212268267136321</v>
       </c>
       <c r="J9" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="K9" t="n">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009949169339719122</v>
+        <v>0.0007881347902174429</v>
       </c>
       <c r="M9" t="n">
-        <v>2.57091589620798</v>
+        <v>2.557781859166397</v>
       </c>
       <c r="N9" t="n">
-        <v>10.66725633676475</v>
+        <v>10.60086706862436</v>
       </c>
       <c r="O9" t="n">
-        <v>3.266076596891865</v>
+        <v>3.255897275502463</v>
       </c>
       <c r="P9" t="n">
-        <v>397.8104760813545</v>
+        <v>397.8270079165187</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27102,7 +27286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J557"/>
+  <dimension ref="A1:J561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56061,6 +56245,214 @@
         </is>
       </c>
     </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-35.0210864203325,173.86594041812702</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-35.0209795583183,173.86682733529102</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-35.02086193730671,173.8677084838284</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-35.02072629932814,173.86854622720617</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>-35.020533605947065,173.8693596582845</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>-35.02024050819944,173.87012856826536</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>-35.01986176260886,173.87079604730633</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>-35.01936129019635,173.8713491786143</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-35.02109973186226,173.86594156186672</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-35.020988989539156,173.8668283425441</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-35.02086426685026,173.86770880356218</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-35.02072901844598,173.86854701446802</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>-35.020533354311915,173.86935953763646</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>-35.02024319530854,173.8701303621655</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>-35.01986115865225,173.87079538845146</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>-35.01935796209145,173.8713444179218</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-35.02109631403707,173.86594126820378</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-35.02098449848161,173.86682786289975</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-35.02086274368717,173.86770859450547</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-35.02072489591246,173.86854582087747</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>-35.02053050244696,173.86935817029192</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>-35.020240192068954,173.87012835721828</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-35.019860017845296,173.87079414394782</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>-35.01935615206941,173.87134182877335</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-35.02109478500998,173.86594113682827</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-35.02098054635096,173.86682744081273</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-35.02086077253495,173.86770832396155</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-35.02072524676638,173.86854592245962</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>-35.02052832160906,173.8693571246756</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>-35.020240192068954,173.87012835721828</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>-35.01986095733338,173.87079516883315</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>-35.01935556819132,173.87134099356422</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0051/nzd0051.xlsx
+++ b/data/nzd0051/nzd0051.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J561"/>
+  <dimension ref="A1:J564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20634,6 +20634,114 @@
         <v>397.42</v>
       </c>
       <c r="J561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>380</v>
+      </c>
+      <c r="C562" t="n">
+        <v>387</v>
+      </c>
+      <c r="D562" t="n">
+        <v>392.23</v>
+      </c>
+      <c r="E562" t="n">
+        <v>399.15</v>
+      </c>
+      <c r="F562" t="n">
+        <v>395.11</v>
+      </c>
+      <c r="G562" t="n">
+        <v>397.33</v>
+      </c>
+      <c r="H562" t="n">
+        <v>398.77</v>
+      </c>
+      <c r="I562" t="n">
+        <v>397.39</v>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>380.2</v>
+      </c>
+      <c r="C563" t="n">
+        <v>386.66</v>
+      </c>
+      <c r="D563" t="n">
+        <v>392.4</v>
+      </c>
+      <c r="E563" t="n">
+        <v>399.1</v>
+      </c>
+      <c r="F563" t="n">
+        <v>395.17</v>
+      </c>
+      <c r="G563" t="n">
+        <v>397.28</v>
+      </c>
+      <c r="H563" t="n">
+        <v>399.1</v>
+      </c>
+      <c r="I563" t="n">
+        <v>397.09</v>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="C564" t="n">
+        <v>388.31</v>
+      </c>
+      <c r="D564" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="E564" t="n">
+        <v>400.21</v>
+      </c>
+      <c r="F564" t="n">
+        <v>395.69</v>
+      </c>
+      <c r="G564" t="n">
+        <v>397.92</v>
+      </c>
+      <c r="H564" t="n">
+        <v>399.52</v>
+      </c>
+      <c r="I564" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="J564" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20650,7 +20758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B586"/>
+  <dimension ref="A1:B589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26513,6 +26621,36 @@
       </c>
       <c r="B586" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -26681,28 +26819,28 @@
         <v>0.097</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1240900159193603</v>
+        <v>0.1202920877890832</v>
       </c>
       <c r="J2" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K2" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03930390971321052</v>
+        <v>0.03733744380564252</v>
       </c>
       <c r="M2" t="n">
-        <v>3.757736968087563</v>
+        <v>3.754057745975815</v>
       </c>
       <c r="N2" t="n">
-        <v>21.37906920281385</v>
+        <v>21.33558913358801</v>
       </c>
       <c r="O2" t="n">
-        <v>4.623750555859804</v>
+        <v>4.619046344602748</v>
       </c>
       <c r="P2" t="n">
-        <v>380.8828921013596</v>
+        <v>380.9221736250803</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26759,28 +26897,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1880378235898751</v>
+        <v>0.183867348273478</v>
       </c>
       <c r="J3" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K3" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1589001457599236</v>
+        <v>0.1535354364233821</v>
       </c>
       <c r="M3" t="n">
-        <v>2.509951421271341</v>
+        <v>2.518551883051703</v>
       </c>
       <c r="N3" t="n">
-        <v>10.63110815930973</v>
+        <v>10.65885110818223</v>
       </c>
       <c r="O3" t="n">
-        <v>3.260538016847792</v>
+        <v>3.264789596311259</v>
       </c>
       <c r="P3" t="n">
-        <v>386.2482987460758</v>
+        <v>386.2914351535105</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26837,28 +26975,28 @@
         <v>0.1301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1576692540088065</v>
+        <v>0.1552544704334593</v>
       </c>
       <c r="J4" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K4" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1421238067550366</v>
+        <v>0.1394554579584519</v>
       </c>
       <c r="M4" t="n">
-        <v>1.870637609459106</v>
+        <v>1.870844746743957</v>
       </c>
       <c r="N4" t="n">
-        <v>8.523474238829706</v>
+        <v>8.506033389302912</v>
       </c>
       <c r="O4" t="n">
-        <v>2.919498970513555</v>
+        <v>2.916510481603471</v>
       </c>
       <c r="P4" t="n">
-        <v>390.6194928746608</v>
+        <v>390.6444695523052</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26915,28 +27053,28 @@
         <v>0.1363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2055590174277734</v>
+        <v>0.2017535777230906</v>
       </c>
       <c r="J5" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K5" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2428789992557634</v>
+        <v>0.2365816156201788</v>
       </c>
       <c r="M5" t="n">
-        <v>2.202703298399464</v>
+        <v>2.209317160821342</v>
       </c>
       <c r="N5" t="n">
-        <v>7.481923041870653</v>
+        <v>7.511473288705911</v>
       </c>
       <c r="O5" t="n">
-        <v>2.735310410514802</v>
+        <v>2.740706713369001</v>
       </c>
       <c r="P5" t="n">
-        <v>397.5997743430851</v>
+        <v>397.639135535364</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26993,28 +27131,28 @@
         <v>0.1141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1013666920292724</v>
+        <v>0.09980558098045911</v>
       </c>
       <c r="J6" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K6" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06752774446617893</v>
+        <v>0.06625394962944375</v>
       </c>
       <c r="M6" t="n">
-        <v>2.316810928932479</v>
+        <v>2.311534866946977</v>
       </c>
       <c r="N6" t="n">
-        <v>8.059517931677675</v>
+        <v>8.028375468649617</v>
       </c>
       <c r="O6" t="n">
-        <v>2.838929011383989</v>
+        <v>2.833438806229917</v>
       </c>
       <c r="P6" t="n">
-        <v>394.0912788677278</v>
+        <v>394.1074255371381</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27071,28 +27209,28 @@
         <v>0.1124</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02331824556320504</v>
+        <v>0.02299993491485654</v>
       </c>
       <c r="J7" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K7" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003254798743145715</v>
+        <v>0.003204950890623559</v>
       </c>
       <c r="M7" t="n">
-        <v>2.486284620800356</v>
+        <v>2.474995865849713</v>
       </c>
       <c r="N7" t="n">
-        <v>9.458376545238412</v>
+        <v>9.408897202044972</v>
       </c>
       <c r="O7" t="n">
-        <v>3.075447373186284</v>
+        <v>3.067392573839379</v>
       </c>
       <c r="P7" t="n">
-        <v>397.1879818137725</v>
+        <v>397.1912724720228</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27149,28 +27287,28 @@
         <v>0.0858</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005493376829237027</v>
+        <v>0.00198688538372262</v>
       </c>
       <c r="J8" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K8" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L8" t="n">
-        <v>1.800093146875348e-06</v>
+        <v>2.380884543928818e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.413826895468112</v>
+        <v>2.408295949189835</v>
       </c>
       <c r="N8" t="n">
-        <v>9.538275306910426</v>
+        <v>9.497584247162944</v>
       </c>
       <c r="O8" t="n">
-        <v>3.088409834673894</v>
+        <v>3.081815089709787</v>
       </c>
       <c r="P8" t="n">
-        <v>397.7555186429801</v>
+        <v>397.7406544010714</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27227,28 +27365,28 @@
         <v>0.0939</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01212268267136321</v>
+        <v>0.01097017334457978</v>
       </c>
       <c r="J9" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K9" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0007881347902174429</v>
+        <v>0.0006529318636323556</v>
       </c>
       <c r="M9" t="n">
-        <v>2.557781859166397</v>
+        <v>2.547877462464524</v>
       </c>
       <c r="N9" t="n">
-        <v>10.60086706862436</v>
+        <v>10.55095231907106</v>
       </c>
       <c r="O9" t="n">
-        <v>3.255897275502463</v>
+        <v>3.248222947870276</v>
       </c>
       <c r="P9" t="n">
-        <v>397.8270079165187</v>
+        <v>397.8389251815867</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27286,7 +27424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J561"/>
+  <dimension ref="A1:J564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56453,6 +56591,162 @@
         </is>
       </c>
     </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-35.02108902867279,173.86594064223814</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-35.02097874992794,173.86682724895505</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-35.02085987655666,173.86770820098704</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>-35.02072129965982,173.86854477966028</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>-35.020523540541284,173.86935483236306</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>-35.020238690449155,173.87012735474474</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>-35.01985961520753,173.87079370471122</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>-35.01935574335475,173.87134124412697</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-35.02108722981742,173.86594048767876</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>-35.02098180384708,173.86682757511315</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-35.02085835339357,173.86770799193036</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>-35.02072173822722,173.868544906638</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>-35.02052303727099,173.869354591067</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>-35.02023908561226,173.87012761855357</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>-35.01985740069986,173.87079128891017</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>-35.019357494988995,173.87134374975443</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-35.02107463782976,173.86593940576319</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>-35.02096698335713,173.8668259922873</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>-35.02085288792602,173.86770724178592</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>-35.02071200203095,173.86854208773337</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>-35.020518675595085,173.86935249983478</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>-35.02023402752446,173.8701242418008</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>-35.01985458223547,173.87078821425445</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>-35.01935977211345,173.8713470070703</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0051/nzd0051.xlsx
+++ b/data/nzd0051/nzd0051.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J564"/>
+  <dimension ref="A1:J568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20742,6 +20742,150 @@
         <v>396.7</v>
       </c>
       <c r="J564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>379.63</v>
+      </c>
+      <c r="C565" t="n">
+        <v>386.86</v>
+      </c>
+      <c r="D565" t="n">
+        <v>391.53</v>
+      </c>
+      <c r="E565" t="n">
+        <v>398.81</v>
+      </c>
+      <c r="F565" t="n">
+        <v>394.14</v>
+      </c>
+      <c r="G565" t="n">
+        <v>395.75</v>
+      </c>
+      <c r="H565" t="n">
+        <v>397.58</v>
+      </c>
+      <c r="I565" t="n">
+        <v>395.38</v>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>380.2</v>
+      </c>
+      <c r="C566" t="n">
+        <v>387.17</v>
+      </c>
+      <c r="D566" t="n">
+        <v>392.13</v>
+      </c>
+      <c r="E566" t="n">
+        <v>399.58</v>
+      </c>
+      <c r="F566" t="n">
+        <v>394.09</v>
+      </c>
+      <c r="G566" t="n">
+        <v>395.68</v>
+      </c>
+      <c r="H566" t="n">
+        <v>397.64</v>
+      </c>
+      <c r="I566" t="n">
+        <v>395.07</v>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>380.8</v>
+      </c>
+      <c r="C567" t="n">
+        <v>387.8</v>
+      </c>
+      <c r="D567" t="n">
+        <v>392.62</v>
+      </c>
+      <c r="E567" t="n">
+        <v>400.08</v>
+      </c>
+      <c r="F567" t="n">
+        <v>394.8</v>
+      </c>
+      <c r="G567" t="n">
+        <v>396.26</v>
+      </c>
+      <c r="H567" t="n">
+        <v>397.79</v>
+      </c>
+      <c r="I567" t="n">
+        <v>395.53</v>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>382.01</v>
+      </c>
+      <c r="C568" t="n">
+        <v>388.46</v>
+      </c>
+      <c r="D568" t="n">
+        <v>393.46</v>
+      </c>
+      <c r="E568" t="n">
+        <v>400.25</v>
+      </c>
+      <c r="F568" t="n">
+        <v>395.17</v>
+      </c>
+      <c r="G568" t="n">
+        <v>396.28</v>
+      </c>
+      <c r="H568" t="n">
+        <v>398.06</v>
+      </c>
+      <c r="I568" t="n">
+        <v>395.73</v>
+      </c>
+      <c r="J568" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20758,7 +20902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B589"/>
+  <dimension ref="A1:B593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26651,6 +26795,46 @@
       </c>
       <c r="B589" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -26819,28 +27003,28 @@
         <v>0.097</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1202920877890832</v>
+        <v>0.1154560388292048</v>
       </c>
       <c r="J2" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="K2" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03733744380564252</v>
+        <v>0.03489063845386031</v>
       </c>
       <c r="M2" t="n">
-        <v>3.754057745975815</v>
+        <v>3.748670136134872</v>
       </c>
       <c r="N2" t="n">
-        <v>21.33558913358801</v>
+        <v>21.27449176104803</v>
       </c>
       <c r="O2" t="n">
-        <v>4.619046344602748</v>
+        <v>4.612427968114845</v>
       </c>
       <c r="P2" t="n">
-        <v>380.9221736250803</v>
+        <v>380.972378974525</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26897,28 +27081,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.183867348273478</v>
+        <v>0.1788049192186768</v>
       </c>
       <c r="J3" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="K3" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1535354364233821</v>
+        <v>0.1473032702599949</v>
       </c>
       <c r="M3" t="n">
-        <v>2.518551883051703</v>
+        <v>2.527726758338429</v>
       </c>
       <c r="N3" t="n">
-        <v>10.65885110818223</v>
+        <v>10.67823341406771</v>
       </c>
       <c r="O3" t="n">
-        <v>3.264789596311259</v>
+        <v>3.267756633237504</v>
       </c>
       <c r="P3" t="n">
-        <v>386.2914351535105</v>
+        <v>386.3439937663563</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26975,28 +27159,28 @@
         <v>0.1301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1552544704334593</v>
+        <v>0.1519690382825678</v>
       </c>
       <c r="J4" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="K4" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1394554579584519</v>
+        <v>0.1356824877159787</v>
       </c>
       <c r="M4" t="n">
-        <v>1.870844746743957</v>
+        <v>1.871994862934969</v>
       </c>
       <c r="N4" t="n">
-        <v>8.506033389302912</v>
+        <v>8.488247232286758</v>
       </c>
       <c r="O4" t="n">
-        <v>2.916510481603471</v>
+        <v>2.913459667180371</v>
       </c>
       <c r="P4" t="n">
-        <v>390.6444695523052</v>
+        <v>390.6785761778191</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27053,28 +27237,28 @@
         <v>0.1363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2017535777230906</v>
+        <v>0.1970828710929709</v>
       </c>
       <c r="J5" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="K5" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2365816156201788</v>
+        <v>0.2291481329929358</v>
       </c>
       <c r="M5" t="n">
-        <v>2.209317160821342</v>
+        <v>2.217194250987706</v>
       </c>
       <c r="N5" t="n">
-        <v>7.511473288705911</v>
+        <v>7.538946161321895</v>
       </c>
       <c r="O5" t="n">
-        <v>2.740706713369001</v>
+        <v>2.745714144138442</v>
       </c>
       <c r="P5" t="n">
-        <v>397.639135535364</v>
+        <v>397.6876274698502</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27131,28 +27315,28 @@
         <v>0.1141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09980558098045911</v>
+        <v>0.09670868354059062</v>
       </c>
       <c r="J6" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="K6" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06625394962944375</v>
+        <v>0.06313417937990673</v>
       </c>
       <c r="M6" t="n">
-        <v>2.311534866946977</v>
+        <v>2.309243862841196</v>
       </c>
       <c r="N6" t="n">
-        <v>8.028375468649617</v>
+        <v>8.007594517439186</v>
       </c>
       <c r="O6" t="n">
-        <v>2.833438806229917</v>
+        <v>2.829769339970872</v>
       </c>
       <c r="P6" t="n">
-        <v>394.1074255371381</v>
+        <v>394.1395775348355</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27209,28 +27393,28 @@
         <v>0.1124</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02299993491485654</v>
+        <v>0.02048297944086226</v>
       </c>
       <c r="J7" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="K7" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003204950890623559</v>
+        <v>0.002577977032903411</v>
       </c>
       <c r="M7" t="n">
-        <v>2.474995865849713</v>
+        <v>2.469945226485838</v>
       </c>
       <c r="N7" t="n">
-        <v>9.408897202044972</v>
+        <v>9.365790585640701</v>
       </c>
       <c r="O7" t="n">
-        <v>3.067392573839379</v>
+        <v>3.060357917897954</v>
       </c>
       <c r="P7" t="n">
-        <v>397.1912724720228</v>
+        <v>397.2174045840059</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27287,28 +27471,28 @@
         <v>0.0858</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00198688538372262</v>
+        <v>0.00194680012822205</v>
       </c>
       <c r="J8" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="K8" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L8" t="n">
-        <v>2.380884543928818e-05</v>
+        <v>2.322483676220344e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.408295949189835</v>
+        <v>2.392404243964309</v>
       </c>
       <c r="N8" t="n">
-        <v>9.497584247162944</v>
+        <v>9.430710244457108</v>
       </c>
       <c r="O8" t="n">
-        <v>3.081815089709787</v>
+        <v>3.070946148088095</v>
       </c>
       <c r="P8" t="n">
-        <v>397.7406544010714</v>
+        <v>397.7410686847547</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27365,28 +27549,28 @@
         <v>0.0939</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01097017334457978</v>
+        <v>0.007221891136282774</v>
       </c>
       <c r="J9" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="K9" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0006529318636323556</v>
+        <v>0.000286236730350331</v>
       </c>
       <c r="M9" t="n">
-        <v>2.547877462464524</v>
+        <v>2.541863019803412</v>
       </c>
       <c r="N9" t="n">
-        <v>10.55095231907106</v>
+        <v>10.52729055649735</v>
       </c>
       <c r="O9" t="n">
-        <v>3.248222947870276</v>
+        <v>3.244578640824931</v>
       </c>
       <c r="P9" t="n">
-        <v>397.8389251815867</v>
+        <v>397.8778197332722</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27424,7 +27608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J564"/>
+  <dimension ref="A1:J568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56747,6 +56931,214 @@
         </is>
       </c>
     </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-35.02109235655524,173.86594092817305</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>-35.02098000742406,173.86682738325544</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>-35.02086614840466,173.86770906180868</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-35.02072428191811,173.86854564310866</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>-35.0205316767443,173.86935873331612</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>-35.020251177603,173.87013569110485</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>-35.019867600855996,173.8708024162374</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>-35.01936747930317,173.87135803183304</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-35.02108722981742,173.86594048767876</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>-35.02097722296838,173.866827085876</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>-35.02086077253495,173.86770832396155</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>-35.020717527980196,173.8685436876521</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>-35.02053209613621,173.8693589343962</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>-35.02025173083132,173.87013606043732</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>-35.019867198218265,173.87080197700072</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>-35.01936928932486,173.8713606209822</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-35.02108183325129,173.8659400240006</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>-35.02097156423584,173.86682648152433</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>-35.02085638224134,173.86770772138647</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>-35.02071314230619,173.8685424178753</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>-35.02052614077113,173.8693560790593</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>-35.02024714693949,173.87013300025413</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>-35.01986619162396,173.87080087890914</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>-35.01936660348622,173.871356779019</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>-35.02107095017623,173.86593908891655</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>-35.02096563603985,173.86682584839406</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>-35.02084885602372,173.86770668840077</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>-35.02071165117703,173.86854198615123</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>-35.02052303727099,173.869354591067</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>-35.02024698887424,173.87013289473057</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>-35.01986437975418,173.8707989023443</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>-35.019365435730236,173.8713551086003</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
